--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M7B6_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M7B6_IN_Piura.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>0.04</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>5.1</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C13" s="31">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>57.23</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>37.63</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1921,11 +1921,11 @@
       </c>
       <c r="B15" s="45">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>91.2852</v>
       </c>
       <c r="C15" s="46">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
@@ -1946,11 +1946,11 @@
       </c>
       <c r="B16" s="48">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>0.0325</v>
       </c>
       <c r="C16" s="49">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>0.04</v>
       </c>
       <c r="D16" s="47" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B17" s="48">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>91.2527</v>
       </c>
       <c r="C17" s="49">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>99.96</v>
       </c>
       <c r="D17" s="47" t="inlineStr">
         <is>
@@ -2169,11 +2169,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>91.3171</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2292,6 +2292,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2531,6 +2532,7 @@
       <c r="F16" s="17" t="inlineStr"/>
       <c r="G16" s="17" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -2575,6 +2577,7 @@
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="108" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -2860,11 +2863,11 @@
       </c>
       <c r="B14" s="33">
         <f>SUM(B10:B13)</f>
-        <v/>
+        <v>402.84</v>
       </c>
       <c r="C14" s="23">
         <f>SUM(C10:C13)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -2874,19 +2877,19 @@
       <c r="E14" s="17" t="inlineStr"/>
       <c r="F14" s="17">
         <f>ROUND(AVERAGE(F10:F13),2)</f>
-        <v/>
+        <v>16.96</v>
       </c>
       <c r="G14" s="22">
         <f>ROUND(AVERAGE(G10:G13),4)</f>
-        <v/>
+        <v>0.2968</v>
       </c>
       <c r="H14" s="23">
         <f>ROUND(AVERAGE(H10:H13),2)</f>
-        <v/>
+        <v>1.81</v>
       </c>
       <c r="I14" s="23">
         <f>ROUND(AVERAGE(I10:I13),2)</f>
-        <v/>
+        <v>99.79</v>
       </c>
     </row>
     <row r="15"/>
